--- a/01_Data/00_Inputs/MUNICIPIOS_SUBREG_PROV.xlsx
+++ b/01_Data/00_Inputs/MUNICIPIOS_SUBREG_PROV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Personal\Laboral\EAFIT\Valor Público\2026\Provincias\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IA Provincias\Proyecto datos y tablas 2\01_Data\00_Inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9157FBD2-2EA2-46BA-9A2D-57E2C1B99391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BDA7F93-A754-41B0-80C3-FE325BBB4364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{05B6BA55-3C5B-484A-9D2D-6F59C5FEA997}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{05B6BA55-3C5B-484A-9D2D-6F59C5FEA997}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$126</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -852,13 +852,13 @@
     <t>PROVINCIA DE SAN JUAN</t>
   </si>
   <si>
-    <t>POVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
-  </si>
-  <si>
     <t>PROVINCIA MINERO AGROECOLOGICA</t>
   </si>
   <si>
     <t>PROVINCIA DEL RIO GRANDE</t>
+  </si>
+  <si>
+    <t>PROVINCIA DEL AGUA, BOSQUES Y TURISMO</t>
   </si>
 </sst>
 </file>
@@ -1309,7 +1309,7 @@
         <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -1493,7 +1493,7 @@
         <v>255</v>
       </c>
       <c r="D18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -1727,7 +1727,7 @@
         <v>257</v>
       </c>
       <c r="D36" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -1741,7 +1741,7 @@
         <v>257</v>
       </c>
       <c r="D37" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -1797,7 +1797,7 @@
         <v>255</v>
       </c>
       <c r="D41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -1858,7 +1858,7 @@
         <v>255</v>
       </c>
       <c r="D46" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -1956,7 +1956,7 @@
         <v>257</v>
       </c>
       <c r="D53" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -1995,7 +1995,7 @@
         <v>257</v>
       </c>
       <c r="D56" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -2168,7 +2168,7 @@
         <v>257</v>
       </c>
       <c r="D69" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -2282,7 +2282,7 @@
         <v>257</v>
       </c>
       <c r="D78" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
@@ -2357,7 +2357,7 @@
         <v>254</v>
       </c>
       <c r="D84" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -2449,7 +2449,7 @@
         <v>257</v>
       </c>
       <c r="D91" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
@@ -2463,7 +2463,7 @@
         <v>257</v>
       </c>
       <c r="D92" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
@@ -2516,7 +2516,7 @@
         <v>257</v>
       </c>
       <c r="D96" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
@@ -2530,7 +2530,7 @@
         <v>255</v>
       </c>
       <c r="D97" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
@@ -2555,7 +2555,7 @@
         <v>257</v>
       </c>
       <c r="D99" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
@@ -2580,7 +2580,7 @@
         <v>257</v>
       </c>
       <c r="D101" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
@@ -2608,7 +2608,7 @@
         <v>255</v>
       </c>
       <c r="D103" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
@@ -2644,7 +2644,7 @@
         <v>254</v>
       </c>
       <c r="D106" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
@@ -2817,7 +2817,7 @@
         <v>254</v>
       </c>
       <c r="D119" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
@@ -2856,7 +2856,7 @@
         <v>254</v>
       </c>
       <c r="D122" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
@@ -2884,7 +2884,7 @@
         <v>254</v>
       </c>
       <c r="D124" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
